--- a/80_인수인계_프로젝트완료 및 유지보수용/08_현업공유_산출물/30_output_share/05_지표GOLD매핑.xlsx
+++ b/80_인수인계_프로젝트완료 및 유지보수용/08_현업공유_산출물/30_output_share/05_지표GOLD매핑.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-18 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-27 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-18</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,990,875/4,778,926 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,990,875/4,778,926 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,990,875/4,778,926 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,884,683/42,791,677 (4.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,887,796/42,981,657 (4.4%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,884,683/42,791,677 (4.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,887,796/42,981,657 (4.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 248,133/272,032 (91.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 249,697/274,105 (91.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 248,133/272,032 (91.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 249,697/274,105 (91.1%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 248,133/272,032 (91.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 249,697/274,105 (91.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 190,712/272,032 (70.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 191,983/274,105 (70.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AGENCY_CONV_MEMBERS` 비영 50,927/272,032 (18.7%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AGENCY_CONV_MEMBERS` 비영 50,621/274,105 (18.5%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,657행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,657행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,657행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,657행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,657행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,657행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,657행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 213,528/272,032 (78.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 215,149/274,105 (78.5%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 190,712/272,032 (70.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 191,983/274,105 (70.0%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,850/272,032 (8.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,726/274,105 (8.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_CAMPAIGN_MONTHLY.STOP_CNT` 비영 206,009/1,686,945 (12.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_CAMPAIGN_MONTHLY.STOP_CNT` 비영 206,708/1,687,032 (12.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 4,110,632/42,981,657 (9.6%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DECREASE_CNT` 비영 117,239/42,791,677 (0.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DECREASE_CNT` 비영 117,537/42,981,657 (0.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,884,683/42,791,677 (4.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,887,796/42,981,657 (4.4%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 비영 37,993,241/42,791,677 (88.8%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 비영 38,154,459/42,981,657 (88.8%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 비영 40,386,853/42,791,677 (94.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 비영 40,573,727/42,981,657 (94.4%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,007,090/42,981,657 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,007,090/42,981,657 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,076,058/4,771,165 (22.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,077,840/4,778,926 (22.6%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,076,058/4,771,165 (22.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,077,840/4,778,926 (22.6%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -4944,12 +4944,12 @@
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,076,058/4,771,165 (22.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,077,840/4,778,926 (22.6%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N68" s="4" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.REGULAR_FEE` 비영 37,557,143/42,791,677 (87.8%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.REGULAR_FEE` 비영 37,557,563/42,981,657 (87.4%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N70" s="4" t="inlineStr"/>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N74" s="4" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.BILLED_AMT` 비영 39,845,615/42,791,677 (93.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.BILLED_AMT` 비영 40,037,011/42,981,657 (93.1%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 4,110,632/42,981,657 (9.6%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N80" s="4" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 4,110,632/42,981,657 (9.6%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 4,110,632/42,981,657 (9.6%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N82" s="4" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 4,110,632/42,981,657 (9.6%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_REASON` 5,904행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_REASON` 5,917행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N86" s="4" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 44,406,102/44,406,102 (100.0%)</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 44,626,415/44,626,415 (100.0%)</t>
         </is>
       </c>
       <c r="N89" s="4" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 26,019,188/44,406,102 (58.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 26,127,308/44,626,415 (58.5%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N90" s="4" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.FAIL_MEMBERS` 비영 2,064,917/44,406,102 (4.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.FAIL_MEMBERS` 비영 2,070,335/44,626,415 (4.6%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.D5_GIFT_PART_AMT` 비영 26,544/44,406,102 (0.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.D5_GIFT_PART_AMT` 비영 26,544/44,626,415 (0.1%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 1,591,255/1,591,255 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 1,651,036/1,651,036 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 46,255행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 49,892행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N103" s="4" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 46,255행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 49,892행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N104" s="4" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 46,255행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 49,892행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N105" s="4" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="M106" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N106" s="4" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 440행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 482행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N107" s="4" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 440행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 482행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N108" s="4" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 323,161/1,591,255 (20.3%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 339,375/1,651,036 (20.6%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
       <c r="N111" s="4" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 440행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 482행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N113" s="4" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="M114" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,801,193행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,803,896행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N114" s="4" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="M115" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,801,193행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,803,896행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N115" s="4" t="inlineStr">
@@ -8870,11 +8870,19 @@
       </c>
       <c r="M116" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,801,193행 실재 — 대응 물리 컬럼 미특정</t>
-        </is>
-      </c>
-      <c r="N116" s="4" t="inlineStr"/>
-      <c r="O116" s="4" t="inlineStr"/>
+          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,803,896행 실재 — 대응 물리 컬럼 미특정</t>
+        </is>
+      </c>
+      <c r="N116" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_SESSION.MEMBER_DK</t>
+        </is>
+      </c>
+      <c r="O116" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -8939,7 +8947,7 @@
       </c>
       <c r="M117" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N117" s="4" t="inlineStr">
@@ -8996,7 +9004,7 @@
       </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_ORG_CLEAN.DEPT_ID</t>
         </is>
       </c>
       <c r="J118" s="4" t="inlineStr">
@@ -9069,7 +9077,7 @@
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_ORG_CLEAN.DEPT_ID</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -9142,7 +9150,7 @@
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_ORG_CLEAN.DEPT_ID</t>
         </is>
       </c>
       <c r="J120" s="4" t="inlineStr">
@@ -9231,7 +9239,7 @@
       </c>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N121" s="4" t="inlineStr">
@@ -9304,7 +9312,7 @@
       </c>
       <c r="M122" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N122" s="4" t="inlineStr">
@@ -9377,7 +9385,7 @@
       </c>
       <c r="M123" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N123" s="4" t="inlineStr">
@@ -9450,7 +9458,7 @@
       </c>
       <c r="M124" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N124" s="4" t="inlineStr">
@@ -10156,7 +10164,7 @@
       </c>
       <c r="M134" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N134" s="4" t="inlineStr">
@@ -10229,7 +10237,7 @@
       </c>
       <c r="M135" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N135" s="4" t="inlineStr">
@@ -10302,7 +10310,7 @@
       </c>
       <c r="M136" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N136" s="4" t="inlineStr">
@@ -10641,8 +10649,16 @@
           <t>DIM_DATE</t>
         </is>
       </c>
-      <c r="I141" s="4" t="inlineStr"/>
-      <c r="J141" s="4" t="inlineStr"/>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="K141" s="4" t="inlineStr"/>
       <c r="L141" s="6" t="inlineStr">
         <is>
@@ -11309,7 +11325,7 @@
       </c>
       <c r="M151" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N151" s="4" t="inlineStr"/>
@@ -11374,7 +11390,7 @@
       </c>
       <c r="M152" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,990,875/4,778,926 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N152" s="4" t="inlineStr">
@@ -11447,7 +11463,7 @@
       </c>
       <c r="M153" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_CAMPAIGN_MONTHLY.DEV_CNT` 비영 76,210/1,686,945 (4.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_INFLOW_ALLOC.DEV_CNT` 비영 1,290/1,426 (90.5%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N153" s="4" t="inlineStr">
@@ -11520,7 +11536,7 @@
       </c>
       <c r="M154" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_MEMBERS` 비영 1,859,125/42,791,677 (4.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_MEMBERS` 비영 1,862,172/42,981,657 (4.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N154" s="4" t="inlineStr">
@@ -11593,7 +11609,7 @@
       </c>
       <c r="M155" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_CNT` 비영 1,859,125/42,791,677 (4.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_CNT` 비영 1,862,172/42,981,657 (4.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N155" s="4" t="inlineStr">
@@ -11645,12 +11661,12 @@
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>FTG-B (measure — 컬럼 06_DDL.sql 확인)</t>
+          <t>FTG-B.ANNUAL_GOAL_CNT</t>
         </is>
       </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
-          <t>CRM_BIZ_TARGET.MONTH_KEY</t>
+          <t>CRM_BIZ_TARGET.TARGET_CNT</t>
         </is>
       </c>
       <c r="J156" s="4" t="inlineStr">
@@ -11659,14 +11675,14 @@
         </is>
       </c>
       <c r="K156" s="4" t="inlineStr"/>
-      <c r="L156" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L156" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M156" s="4" t="inlineStr">
         <is>
-          <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_PROJECT` 0행</t>
+          <t>실측: `FACT_TARGET_PROJECT.ANNUAL_GOAL_CNT` 비영 2,966/2,966 (100.0%)</t>
         </is>
       </c>
       <c r="N156" s="4" t="inlineStr">
@@ -11718,12 +11734,12 @@
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>FTG-B (measure — 컬럼 06_DDL.sql 확인)</t>
+          <t>FTG-B.SUPP_GOAL_CNT</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>CRM_BIZ_TARGET.MONTH_KEY</t>
+          <t>CRM_BIZ_TARGET.TARGET_CNT</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
@@ -11739,7 +11755,7 @@
       </c>
       <c r="M157" s="4" t="inlineStr">
         <is>
-          <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_PROJECT` 0행</t>
+          <t>실측: `FACT_TARGET_PROJECT.SUPP_GOAL_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
       <c r="N157" s="4" t="inlineStr"/>
@@ -11783,12 +11799,12 @@
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>FTG-B (measure — 컬럼 06_DDL.sql 확인)</t>
+          <t>FTG-B.ANNUAL_CUM_GOAL_CNT</t>
         </is>
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>CRM_BIZ_TARGET.MONTH_KEY</t>
+          <t>CRM_BIZ_TARGET.TARGET_CNT</t>
         </is>
       </c>
       <c r="J158" s="4" t="inlineStr">
@@ -11804,7 +11820,7 @@
       </c>
       <c r="M158" s="4" t="inlineStr">
         <is>
-          <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_PROJECT` 0행</t>
+          <t>실측: `FACT_TARGET_PROJECT.ANNUAL_CUM_GOAL_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
       <c r="N158" s="4" t="inlineStr">
@@ -11856,12 +11872,12 @@
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>FTG-B (measure — 컬럼 06_DDL.sql 확인)</t>
+          <t>FTG-B.SUPP_CUM_GOAL_CNT</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>CRM_BIZ_TARGET.MONTH_KEY</t>
+          <t>CRM_BIZ_TARGET.TARGET_CNT</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -11877,7 +11893,7 @@
       </c>
       <c r="M159" s="4" t="inlineStr">
         <is>
-          <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_PROJECT` 0행</t>
+          <t>실측: `FACT_TARGET_PROJECT.SUPP_CUM_GOAL_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
       <c r="N159" s="4" t="inlineStr"/>
@@ -11942,7 +11958,7 @@
       </c>
       <c r="M160" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 비영 41,122,461/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 비영 41,310,673/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N160" s="4" t="inlineStr">
@@ -12015,7 +12031,7 @@
       </c>
       <c r="M161" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N161" s="4" t="inlineStr">
@@ -12161,7 +12177,7 @@
       </c>
       <c r="M163" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CUM_CNT` 비영 41,615,513/42,791,677 (97.3%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CUM_CNT` 비영 41,805,091/42,981,657 (97.3%)</t>
         </is>
       </c>
       <c r="N163" s="4" t="inlineStr">
@@ -12380,7 +12396,7 @@
       </c>
       <c r="M166" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_REASON` 5,904행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_REASON` 5,917행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N166" s="4" t="inlineStr">
@@ -12672,7 +12688,7 @@
       </c>
       <c r="M170" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,990,875/4,778,926 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N170" s="4" t="inlineStr">
@@ -13171,7 +13187,7 @@
       </c>
       <c r="M177" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N177" s="4" t="inlineStr">
@@ -13248,7 +13264,7 @@
       </c>
       <c r="M178" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N178" s="4" t="inlineStr">
@@ -13325,7 +13341,7 @@
       </c>
       <c r="M179" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N179" s="4" t="inlineStr">
@@ -13402,7 +13418,7 @@
       </c>
       <c r="M180" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N180" s="4" t="inlineStr">
@@ -13459,12 +13475,12 @@
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K181" s="4" t="inlineStr">
@@ -13479,7 +13495,7 @@
       </c>
       <c r="M181" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,007,090/42,981,657 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N181" s="4" t="inlineStr">
@@ -13536,12 +13552,12 @@
       </c>
       <c r="I182" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J182" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K182" s="4" t="inlineStr">
@@ -13556,7 +13572,7 @@
       </c>
       <c r="M182" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,007,090/42,981,657 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N182" s="4" t="inlineStr">
@@ -13613,12 +13629,12 @@
       </c>
       <c r="I183" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J183" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K183" s="4" t="inlineStr">
@@ -13633,7 +13649,7 @@
       </c>
       <c r="M183" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,007,090/42,981,657 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N183" s="4" t="inlineStr">
@@ -13690,12 +13706,12 @@
       </c>
       <c r="I184" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J184" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K184" s="4" t="inlineStr">
@@ -13710,7 +13726,7 @@
       </c>
       <c r="M184" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,007,090/42,981,657 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N184" s="4" t="inlineStr">
@@ -13767,12 +13783,12 @@
       </c>
       <c r="I185" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J185" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K185" s="4" t="inlineStr">
@@ -13787,7 +13803,7 @@
       </c>
       <c r="M185" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,007,090/42,981,657 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N185" s="4" t="inlineStr">
@@ -13864,7 +13880,7 @@
       </c>
       <c r="M186" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,242,457/42,791,677 (2.9%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,244,416/42,981,657 (2.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N186" s="4" t="inlineStr">
@@ -13941,7 +13957,7 @@
       </c>
       <c r="M187" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,242,457/42,791,677 (2.9%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,244,416/42,981,657 (2.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N187" s="4" t="inlineStr">
@@ -14018,7 +14034,7 @@
       </c>
       <c r="M188" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N188" s="4" t="inlineStr">
@@ -14095,7 +14111,7 @@
       </c>
       <c r="M189" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N189" s="4" t="inlineStr">
@@ -14172,7 +14188,7 @@
       </c>
       <c r="M190" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N190" s="4" t="inlineStr">
@@ -14249,7 +14265,7 @@
       </c>
       <c r="M191" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N191" s="4" t="inlineStr">
@@ -14326,7 +14342,7 @@
       </c>
       <c r="M192" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N192" s="4" t="inlineStr">
@@ -14634,7 +14650,7 @@
       </c>
       <c r="M196" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 44,406,102/44,406,102 (100.0%)</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 44,626,415/44,626,415 (100.0%)</t>
         </is>
       </c>
       <c r="N196" s="4" t="inlineStr">
@@ -14711,7 +14727,7 @@
       </c>
       <c r="M197" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 26,019,188/44,406,102 (58.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 26,127,308/44,626,415 (58.5%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N197" s="4" t="inlineStr">
@@ -14857,7 +14873,7 @@
       </c>
       <c r="M199" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,987,631/4,771,165 (41.7%) · GA↔CRM identity 커버리지 종속</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,990,875/4,778,926 (41.7%) · GA↔CRM identity 커버리지 종속</t>
         </is>
       </c>
       <c r="N199" s="4" t="inlineStr">
@@ -16295,7 +16311,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-18</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -19417,7 +19433,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-18</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-27</t>
         </is>
       </c>
     </row>
